--- a/output/Monthly_Closing_Report_2025_12.xlsx
+++ b/output/Monthly_Closing_Report_2025_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,22 +474,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>182828000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9240000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>422000</v>
       </c>
       <c r="F2" t="n">
         <v>1280000</v>
       </c>
       <c r="G2" t="n">
-        <v>1280000</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>545875</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -520,78 +520,101 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>원료 합계 (내자+외자)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>183373875</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9240000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>422000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>858000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>내자 자재 (ROH2)</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36299505</v>
-      </c>
-      <c r="G4" t="n">
-        <v>36299505</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>당월 금액</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>원료 합계 (내자+외자)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1280000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B5" t="n">
+        <v>12295459533</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1588552011</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1569014611</v>
+      </c>
+      <c r="E5" t="n">
+        <v>916953371</v>
+      </c>
+      <c r="F5" t="n">
+        <v>49444961</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-867508410</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>내자 합계 (원료+자재)</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>37579505</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>총 매입 합계</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>37579505</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>⚠️ 미분류(매칭실패)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>15605016</v>
+      <c r="B6" t="n">
+        <v>12478287533</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1597792011</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1570814611</v>
+      </c>
+      <c r="E6" t="n">
+        <v>917375371</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50724961</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-866650410</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>전체 합계 (Total)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12478833408</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1597792011</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1570814611</v>
+      </c>
+      <c r="E7" t="n">
+        <v>917375371</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50724961</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-866650410</v>
       </c>
     </row>
   </sheetData>
@@ -605,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,31 +652,51 @@
           <t>금액</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>관련 PO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>엑셀 행</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>최대 지출 품목</t>
+          <t>원료(ROH1) 최다 지출</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2301390</t>
+          <t>1000600</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>나보타 무코팅 바이알</t>
+          <t>Monobasic Sodium Phosphate (나보타전용)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9240000</v>
+        <v>1280000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4500268531.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Top 1</t>
+          <t>자재(ROH2) Top 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -667,47 +710,77 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9240000</v>
+        <v>19096000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4500273848.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-, -, -, -, -, -</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Top 2</t>
+          <t>자재(ROH2) Top 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2003150</t>
+          <t>2001530</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>나보타 Case(100U_미국)</t>
+          <t>(중단)나보타 비닐</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7669101</v>
+        <v>18845309</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4500275817.0, 4500275818.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-, -, -, -</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Top 3</t>
+          <t>자재(ROH2) Top 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2301390</t>
+          <t>2003150</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>나보타 무코팅 바이알</t>
+          <t>나보타 Case(100U_미국)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4620000</v>
+        <v>11503652</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4500274551.0, 4500274552.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-, -, -</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -721,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,28 +807,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1000030</t>
+          <t>2003650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2300340</t>
+          <t>2302130</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2003650</t>
+          <t>1000030</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1001320</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2300980</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2300660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1000590</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>1300010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2300400</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2300340</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2300240</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2001450</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2002960</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2003430</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1301240</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2302210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2301430</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1300610</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2300860</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2301280</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2300820</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1301160</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1300530</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2301710</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2301110</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1301360</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2300680</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2301100</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2302380</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2300100</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2302290</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1000120</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2302470</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2301030</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2301900</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2300130</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1300500</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2302520</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2302980</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1300900</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1301750</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2301670</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1001110</t>
         </is>
       </c>
     </row>
